--- a/jsonlib/Destatis-Daten.xlsx
+++ b/jsonlib/Destatis-Daten.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thoerner/Development/fortune-teller-api/jsonlib/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C22CDB61-C59A-7646-ADE0-D933693E789D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0D9F431-DEB9-4A40-8728-34F30EAC2861}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2980" yWindow="2180" windowWidth="28240" windowHeight="17240" xr2:uid="{6D46B524-5F19-4D46-A283-D289A360C0E0}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="25">
   <si>
     <t>Nahrungsmittel, Getränke und Tabakwaren</t>
   </si>
@@ -111,6 +111,9 @@
   </si>
   <si>
     <t>Jährlich</t>
+  </si>
+  <si>
+    <t>Ausgabenart</t>
   </si>
 </sst>
 </file>
@@ -871,6 +874,9 @@
       <c r="A21" t="s">
         <v>19</v>
       </c>
+      <c r="B21" t="s">
+        <v>24</v>
+      </c>
       <c r="D21" t="s">
         <v>21</v>
       </c>
@@ -1064,5 +1070,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>